--- a/public/hinnakiri.xlsx
+++ b/public/hinnakiri.xlsx
@@ -1,58 +1,269 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Hinnakiri" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Hinnakiri" state="visible" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
+  <si>
+    <t>Willipu OÜ — Hinnakiri</t>
+  </si>
+  <si>
+    <t>Willipu külalisemaja ja karavanipark · Pusi küla, Alatskivi vald</t>
+  </si>
+  <si>
+    <t>Allalaaditud: 29.05.2026</t>
+  </si>
+  <si>
+    <t>Hinnad on informatiivsed ja võivad muutuda. Aktuaalne hinnakiri: willipu.ee</t>
+  </si>
+  <si>
+    <t>Rubriik</t>
+  </si>
+  <si>
+    <t>Kirjeldus</t>
+  </si>
+  <si>
+    <t>Hind</t>
+  </si>
+  <si>
+    <t>Märkus</t>
+  </si>
+  <si>
+    <t>Suur kämpingumaja 🏡</t>
+  </si>
+  <si>
+    <t>5 inimesele</t>
+  </si>
+  <si>
+    <t>110 € / öö</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>4 inimesele</t>
+  </si>
+  <si>
+    <t>100 € / öö</t>
+  </si>
+  <si>
+    <t>2–3 inimesele</t>
+  </si>
+  <si>
+    <t>85 € / öö</t>
+  </si>
+  <si>
+    <t>Väike kämpingumaja 🛖</t>
+  </si>
+  <si>
+    <t>2 inimesele</t>
+  </si>
+  <si>
+    <t>55 € / öö</t>
+  </si>
+  <si>
+    <t>1 inimesele</t>
+  </si>
+  <si>
+    <t>35 € / öö</t>
+  </si>
+  <si>
+    <t>Peamaja — kahene tuba 🛏</t>
+  </si>
+  <si>
+    <t>Peamaja — kolmene tuba 🛏</t>
+  </si>
+  <si>
+    <t>3 inimesele</t>
+  </si>
+  <si>
+    <t>80 € / öö</t>
+  </si>
+  <si>
+    <t>60 € / öö</t>
+  </si>
+  <si>
+    <t>Karavanipark 24/7 🚐</t>
+  </si>
+  <si>
+    <t>Haagissuvila ilma elektrita</t>
+  </si>
+  <si>
+    <t>20 € / öö</t>
+  </si>
+  <si>
+    <t>sisaldab 2 inimest</t>
+  </si>
+  <si>
+    <t>Haagissuvila elektriga</t>
+  </si>
+  <si>
+    <t>25 € / öö</t>
+  </si>
+  <si>
+    <t>Haagissuvila lisa inimene</t>
+  </si>
+  <si>
+    <t>3 € / inimene</t>
+  </si>
+  <si>
+    <t>Telkimine</t>
+  </si>
+  <si>
+    <t>7 € / inimene</t>
+  </si>
+  <si>
+    <t>Muud ❄️</t>
+  </si>
+  <si>
+    <t>Talvine järvetransport</t>
+  </si>
+  <si>
+    <t>küsi hinda</t>
+  </si>
+  <si>
+    <t>Kontakt</t>
+  </si>
+  <si>
+    <t>Telefon</t>
+  </si>
+  <si>
+    <t>+372 56 955 758</t>
+  </si>
+  <si>
+    <t>E-post</t>
+  </si>
+  <si>
+    <t>willipu.willipu@gmail.com</t>
+  </si>
+  <si>
+    <t>Veebileht</t>
+  </si>
+  <si>
+    <t>willipu.ee</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
-    <font>
-      <sz val="12"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="12" x14ac:knownFonts="1">
+    <font>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF4A544D"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FFC89B3C"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF2D4A3E"/>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF4A544D"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF2D4A3E"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF4A544D"/>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1C2620"/>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C2620"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2D4A3E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFE9DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DDD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F4EE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -60,18 +271,173 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFC89B3C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF2D4A3E"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD9D2C2"/>
+      </right>
+      <top style="hair">
+        <color rgb="FFD9D2C2"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FFD9D2C2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFD9D2C2"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD9D2C2"/>
+      </right>
+      <top style="hair">
+        <color rgb="FFD9D2C2"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="FFD9D2C2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF2D4A3E"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD9D2C2"/>
+      </right>
+      <top style="hair">
+        <color rgb="FFD9D2C2"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF2D4A3E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="FFD9D2C2"/>
+      </left>
+      <right style="hair">
+        <color rgb="FFD9D2C2"/>
+      </right>
+      <top style="hair">
+        <color rgb="FFD9D2C2"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF2D4A3E"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="29">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,254 +762,297 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Willipu OÜ — Hinnakiri</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Willipu külalisemaja ja karavanipark, Pusi küla, Alatskivi vald</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Allalaaditud: 29.05.2026</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Hinnad võivad muutuda. Aktuaalne hinnakiri: willipu.ee</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Rubriik</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Kirjeldus</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Hind</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Märkus</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Suur kämpingumaja</v>
-      </c>
-      <c r="B7" t="str">
-        <v>5 inimesele</v>
-      </c>
-      <c r="C7" t="str">
-        <v>110 € / öö</v>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v/>
-      </c>
-      <c r="B8" t="str">
-        <v>4 inimesele</v>
-      </c>
-      <c r="C8" t="str">
-        <v>100 € / öö</v>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v/>
-      </c>
-      <c r="B9" t="str">
-        <v>2–3 inimesele</v>
-      </c>
-      <c r="C9" t="str">
-        <v>85 € / öö</v>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Väike kämpingumaja</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2 inimesele</v>
-      </c>
-      <c r="C11" t="str">
-        <v>55 € / öö</v>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v/>
-      </c>
-      <c r="B12" t="str">
-        <v>1 inimesele</v>
-      </c>
-      <c r="C12" t="str">
-        <v>35 € / öö</v>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Peamaja - kahene tuba</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2 inimesele</v>
-      </c>
-      <c r="C14" t="str">
-        <v>55 € / öö</v>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v/>
-      </c>
-      <c r="B15" t="str">
-        <v>1 inimesele</v>
-      </c>
-      <c r="C15" t="str">
-        <v>35 € / öö</v>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Peamaja - kolmene tuba</v>
-      </c>
-      <c r="B17" t="str">
-        <v>3 inimesele</v>
-      </c>
-      <c r="C17" t="str">
-        <v>80 € / öö</v>
-      </c>
-      <c r="D17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v/>
-      </c>
-      <c r="B18" t="str">
-        <v>2 inimesele</v>
-      </c>
-      <c r="C18" t="str">
-        <v>60 € / öö</v>
-      </c>
-      <c r="D18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Karavanipark 24/7</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Haagissuvila ilma elektrita</v>
-      </c>
-      <c r="C20" t="str">
-        <v>20 € / öö</v>
-      </c>
-      <c r="D20" t="str">
-        <v>sisaldab 2 inimest</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v/>
-      </c>
-      <c r="B21" t="str">
-        <v>Haagissuvila elektriga</v>
-      </c>
-      <c r="C21" t="str">
-        <v>25 € / öö</v>
-      </c>
-      <c r="D21" t="str">
-        <v>sisaldab 2 inimest</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v/>
-      </c>
-      <c r="B22" t="str">
-        <v>Haagissuvila lisa inimene</v>
-      </c>
-      <c r="C22" t="str">
-        <v>3 € / inimene</v>
-      </c>
-      <c r="D22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v/>
-      </c>
-      <c r="B23" t="str">
-        <v>Telkimine</v>
-      </c>
-      <c r="C23" t="str">
-        <v>7 € / inimene</v>
-      </c>
-      <c r="D23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Muud</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Talvine järvetransport</v>
-      </c>
-      <c r="C25" t="str">
-        <v>küsi hinda</v>
-      </c>
-      <c r="D25" t="str">
-        <v/>
-      </c>
+    <row r="1" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="13"/>
+      <c r="B15" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="13">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
   </mergeCells>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/public/hinnakiri.xlsx
+++ b/public/hinnakiri.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
-  <si>
-    <t>Willipu OÜ — Hinnakiri</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
+  <si>
+    <t>OÜ Willipu Turism — Hinnakiri</t>
   </si>
   <si>
     <t>Willipu külalisemaja ja karavanipark · Pusi küla, Alatskivi vald</t>
@@ -131,6 +131,12 @@
   </si>
   <si>
     <t>Kontakt</t>
+  </si>
+  <si>
+    <t>Ettevõte</t>
+  </si>
+  <si>
+    <t>OÜ Willipu Turism</t>
   </si>
   <si>
     <t>Telefon</t>
@@ -763,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1036,8 +1042,18 @@
       <c r="C25" s="28"/>
       <c r="D25" s="28"/>
     </row>
+    <row r="26" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
@@ -1051,6 +1067,7 @@
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
